--- a/data/daily/2026-10/2026-10-13.xlsx
+++ b/data/daily/2026-10/2026-10-13.xlsx
@@ -11,7 +11,9 @@
     <sheet name="카카오선물하기_카드형" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="다이소몰" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="다이소몰_카드형" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="카테고리통계" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="올리브영" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="올리브영_카드형" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="카테고리통계" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1243,14 +1245,39 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1265,35 +1292,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1498,9 +1500,264 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
@@ -1518,12 +1775,267 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -1548,7 +2060,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1573,7 +2085,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1598,7 +2110,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1623,7 +2135,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1648,7 +2160,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2084,22 +2596,22 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16258</v>
+        <v>16259</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>피로 회복 체감 — 피곤한 날 섭취 시 활력이 돋고 덜 피곤해지는 느낌을 받음</t>
+          <t>피로 해소 체감 — 섭취 후 덜 피곤하고 활력이 생기는 체감 효과 있음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>선물용 만족도 — 인지도가 높고 고급스러운 이미지라 선물용 및 수령용으로 만족도가 높음</t>
+          <t>선물용으로 적합 — 인지도가 높고 센스 있는 선물로 만족도가 큼</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>소비기한 아쉬움 — 잔여 소비기한이 기대보다 짧은 제품이 배송되어 아쉬움</t>
+          <t>아쉬운 소비기한 — 소비기한이 11개월가량 지난 재고 상품을 수령하여 실망스러움</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -2143,24 +2655,24 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15594</v>
+        <v>15597</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>활력 및 피로 개선 — 피로 누적 시 섭취하면 기운이 나고 자양강장 효과를 체감함</t>
+          <t>편리한 복용 방식 — 물 없이 정제와 액상을 함께 먹을 수 있어 섭취 및 휴대 용이함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>선물 만족도 — 환절기나 시험 응원 등 지인 건강 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>배송 지연 — 배송이 너무 늦게 도착하여 불만족스러움</t>
-        </is>
-      </c>
+          <t>피로 회복 체감 — 누적된 피로가 덜하고 활력 충전되는 느낌을 받음</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>고급스러운 포장 — 남색과 오렌지 포인트 패키지가 깔끔하고 선물용으로 고급스러움</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -2206,20 +2718,24 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>확실한 피로 개선 — 복용 후 다음 날 피로감이 덜하고 몸에 활력이 생기는 것을 체감함</t>
+          <t>활력 및 피로 개선 — 섭취 다음 날 몸의 활력이 생기고 덜 피곤한 느낌을 받음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>진한 액상 제형 — 다른 액상 비타민 대비 맛이 진하고 섭취하기 좋음</t>
+          <t>진한 액상 제형 — 타사 액상 제품 대비 농도가 진하여 만족스러움</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>선물 및 포장 만족 — 포장이 꼼꼼하여 받는 사람과 주는 사람 모두 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>선물용 만족도 — 포장이 꼼꼼하고 선물용으로 주고받기 적합함</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>다소 아쉬운 맛 — 액상 비타민 특성상 맛 자체는 아쉬움이 있음</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -2265,17 +2781,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 새콤달콤하고 쫀득한 젤리 맛으로 간식처럼 거부감 없이 섭취 가능함</t>
+          <t>맛있는 젤리 제형 — 새콤달콤한 맛과 쫀득한 식감으로 간식처럼 거부감 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>간편한 복용법 — 알약을 잘 삼키지 못하는 사람도 물 없이 쉽게 먹을 수 있음</t>
+          <t>쉬운 복용 편의성 — 알약을 삼키기 어려워하는 사람도 부담 없이 영양을 챙길 수 있음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>귀여운 패키지 — 감귤 손잡이 모양 패키지와 귀여운 사은품으로 선물용으로 좋음</t>
+          <t>귀여운 선물 구성 — 선물 포장과 패키지가 귀엽고 키캡 등 증정품 만족도가 높음</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -2320,22 +2836,22 @@
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 — 복용 후 오후 시간대 눈의 피로나 체력 저하가 줄어들고 에너지가 충전됨</t>
+          <t>빠른 피로 회복 체감 — 복용 후 며칠 지나지 않아 눈의 피로나 체력 저하 완화에 도움을 줌</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>간편한 휴대 섭취 — 개별 포장으로 출근길이나 야외에서 물 없이 바로 섭취 가능함</t>
+          <t>간편한 휴대 및 섭취 — 물 없이 간편하게 먹을 수 있고 개별 포장으로 휴대가 용이함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>배송 포장 아쉬움 — 쇼핑백 미동봉 및 일반 박스 포장으로 배송되어 선물용으로 아쉬움</t>
+          <t>배송 포장 아쉬움 — 쇼핑백 없이 본품 박스만 단독 배송되어 포장 상태가 다소 당황스러움</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -2383,20 +2899,24 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>컨디션 회복 효과 — 섭취 후 다음 날 아침 일어날 때 피로감이 덜하고 개운함</t>
+          <t>간편한 개별 포장 — 외출 시 가방에 챙겨 다니며 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>편리한 휴대성 — 알약과 액상이 세트로 개별 포장되어 외출 시 가방에 넣고 다니기 편함</t>
+          <t>다음 날 컨디션 회복 — 자기 전이나 피로 시 섭취하면 다음 날 아침 컨디션 개선을 체감함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>고급스러운 포장 — 패키지가 깔끔하고 고급스러워 선물용으로 실용적임</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>부담 없는 맛 — 맛이 자극적이거나 거부감 없이 무난함</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>다소 적은 부피감 — 소포장이라 선물용 외형이 풍성해 보이지 않음</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -2442,19 +2962,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>간편한 일일 섭취 — 1병씩 개별 포장되어 출근길이나 일상에서 간편하게 챙겨 먹기 좋음</t>
+          <t>선물용 패키지 만족 — 포장이 깔끔하고 예뻐 명절이나 기념일 선물로 좋음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>고급스러운 포장 — 패키지 포장이 예뻐 명절이나 기념일 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>환절기 활력 충전 — 체력이 떨어지는 환절기 컨디션 및 면역 관리에 도움을 줌</t>
-        </is>
-      </c>
+          <t>환절기 활력 충전 — 출근 시 챙겨 먹기 좋고 환절기 컨디션 및 활력 관리에 유용함</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -2501,17 +3017,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>성별 맞춤 구성 — 남성과 여성용 비타민이 구분되어 있어 맞춤 선택이 가능함</t>
+          <t>성별 맞춤 옵션 — 남성과 여성을 위한 비타민이 각각 구분되어 있어 유용함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>부담 없는 맛 — 비타민 특유의 쓴맛이 없고 진득하여 복용하기 수월함</t>
+          <t>부담 없는 섭취감 — 특유의 쓴맛이 없고 휴대하며 간편하게 복용하기 좋음</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>피로 개선 효과 — 직장인 필수 아이템으로 불릴 만큼 섭취 후 활력과 힘이 남</t>
+          <t>직장인 활력 충전 — 피로할 때 섭취하면 활력 증진에 도움 됨</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -2560,22 +3076,22 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>신선한 혼합 방식 — 버튼을 눌러 분말과 액상을 즉석에서 섞어 먹는 방식이 신선하고 재미있음</t>
+          <t>신선한 혼합 방식 — 캡을 누르면 분말이 액상과 섞이는 독특한 형태로 신선하게 섭취 가능함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 — 섭취 직후 즉각적으로 기운이 나고 피로 회복 체감이 뛰어남</t>
+          <t>빠른 활력 회복 — 복용 후 피로 개선과 에너지 충전 효과를 빠르게 느낌</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>선물용 패키지 — 각 잡힌 박스 포장과 깔끔한 구성으로 선물하기 좋음</t>
+          <t>호불호 없는 맛 — 맛에 거부감이 없고 액상형이라 목넘김이 편함</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>섭취 후 목메임 — 혼합액 음용 후 목이 메여 물을 따로 마셔야 하는 번거로움이 있음</t>
+          <t>음용 시 목 메임 — 혼합액 음용 후 목이 메여 물을 따로 챙겨 마셔야 함</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -2584,7 +3100,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2592,51 +3108,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>올인원 명품비타민 이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 선물</t>
+          <t>고함량 비타민C 고려은단 메가도스C 3000 100포 / 분말비타민C</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7948462</t>
+          <t>https://gift.kakao.com/product/3252731</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260927232309_d6a091055c604810a078748974bfb7eb.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260909091732_b68718856ae342d0b37c3e36916af86b.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>29858</v>
+        <v>956</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>간편한 올인원 섭취 — 물 없이 하루 한 병으로 간편하게 비타민을 보충할 수 있음</t>
+          <t>피로 완화 체감 — 복용 후 덜 피곤하고 피부 및 컨디션 관리에 도움 됨</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>피로 해소 체감 — 복용 후 아침 기상 시 개운함이 다르고 활력이 충전됨</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>선물 포장 및 젤리 증정 — 쇼핑백과 박스 포장이 튼튼하며 추가 젤리 증정 구성에 대한 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>믿을 수 있는 원료 — 영국산 비타민C 원료를 사용하여 브랜드 신뢰도가 높음</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>강한 신맛 — 분말 특성상 맛이 매우 셔서 먹기 부담스러울 수 있음</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -2651,7 +3167,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로저당씬칩+빅맥세트(기프티콘)증정</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2661,46 +3177,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>41,900원</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14208051</t>
+          <t>https://gift.kakao.com/product/13180343</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261013072219_47589b9de86f4b23bd720c4a80a73797.jpg</t>
         </is>
       </c>
       <c r="I12" t="n">
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>244</v>
+        <v>1697</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>달콤하고 맛있는 맛 — 맛이 거부감 없이 달달하여 부담 없이 섭취 가능함</t>
+          <t>소화 편의성 체감 — 섭취 후 더부룩함이 덜하고 속이 편안해지는 느낌을 받음</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>콜라보 디자인 — 리센느 에디션 패키지가 예쁘고 귀여워 소장 및 선물용으로 만족스러움</t>
+          <t>알찬 사은품 혜택 — 프로모션을 통한 단백질칩, 스낵, 기프티콘 등 다양한 증정 구성 만족스러움</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>적은 용량감 — 1포당 양이 다소 적게 느껴져 아쉬움</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>쇼핑백 크기 부적합 — 동봉된 종이가방에 제품을 넣을 때 크기가 타이트하여 잘 들어가지 않음</t>
-        </is>
-      </c>
+          <t>가격 할인 아쉬움 — 평소 상시 판매 가격대에 대한 아쉬움이 있어 세일 요구가 있음</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
     <row r="13" ht="38" customHeight="1">
@@ -2714,7 +3226,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로저당씬칩+빅맥세트(기프티콘)증정</t>
+          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2724,48 +3236,52 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41,900원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180343</t>
+          <t>https://gift.kakao.com/product/14208051</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261013072219_47589b9de86f4b23bd720c4a80a73797.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>1697</v>
+        <v>244</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>속 편한 소화감 — 섭취 후 속 더부룩함이 덜하고 편안해지는 느낌을 받음</t>
+          <t>맛있는 단맛 — 달달하고 맛있어서 부담 없이 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>풍성한 증정품 혜택 — 톡딜 할인 가격에 단백질바, 씬칩, 기프티콘 등 다양한 사은품을 함께 제공함</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>고급스러운 포장 — 선물 포장이 고급스러워 본인 사용 및 지인 선물용으로 모두 만족함</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+          <t>간편한 섭취 방식 — 물과 함께 가볍게 먹기 편함</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>적은 용량 아쉬움 — 맛은 좋으나 1포당 용량이 다소 작게 느껴짐</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>쇼핑백 크기 부적합 — 동봉된 종이가방에 제품을 넣을 때 규격이 빡빡하여 잘 안 들어감</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr"/>
     </row>
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2773,58 +3289,58 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928091559_44d67bbfbab644e3bc688b7716d83f5d.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>755</v>
+        <v>68</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>고급스러운 에디션 포장 — 오간자 패키지와 플리츠백 구성이 고급스러워 선물 개봉 시 만족감이 높음</t>
+          <t>부드럽고 촉촉한 식감 — 닭가슴살 특유의 퍽퍽함 없이 촉촉하고 부드러움</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>맛과 간편함 — 콜라겐 특유의 비린 맛 없이 맛있고 병 타입이라 섭취가 간편함</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>다소 높은 가격대 — 정가 기준 가격대가 비싸 할인 시기에만 구매하게 됨</t>
-        </is>
-      </c>
+          <t>다양하고 맛있는 양념 — 떡볶이맛 등 소스가 다양하고 맛있어 질리지 않음</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>간편한 조리 — 전자레인지로 데우기만 하면 되어 식단 관리에 편리함</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2832,51 +3348,51 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>33,000원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928091559_44d67bbfbab644e3bc688b7716d83f5d.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>68</v>
+        <v>755</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>촉촉하고 맛있는 육질 — 퍽퍽하지 않고 촉촉하며 떡볶이맛 등 다양한 소스가 맛있음</t>
+          <t>고급스러운 선물 포장 — 오간자 패키지와 플리츠백 구성이 매우 예쁘고 고급스러움</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>간편한 조리법 — 전자레인지에 간단히 데워 식단 관리나 간식으로 먹기 편리함</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>높은 가성비 — 할인 행사를 통해 저렴한 가격에 쟁여두기 좋음</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>맛있는 앰플 제형 — 비린 맛 없이 달콤하고 맛있어 매일 섭취하기 좋음</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>비싼 정가 부담 — 평소 가격대가 다소 높아 할인 기간에만 구매하게 됨</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
@@ -2891,58 +3407,58 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +저당단백칩+파로저당견과류바 증정</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>23,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261013104549_cfa2b37d84e542f19a82e0967319903c.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>21</v>
+        <v>908</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>우수한 숙취 해소 — 음주 전후 섭취 시 다음 날 숙취와 몸의 무거움이 확연히 덜함</t>
+          <t>소화 및 배변 도움 — 식후 속 더부룩함이 줄어들고 배변 활동 및 몸이 가벼워지는 느낌을 받음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>간편한 스틱 휴대 — 작은 스틱 포 형태로 가방이나 주머니에 넣어 물 없이 바로 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>고급스러운 선물 패키지 — 보라색 쇼핑백과 리본 손잡이 포장으로 술자리 지인 선물용으로 제격임</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>맛있는 옥수수맛 — 콘스프처럼 달달하고 고소한 맛이라 거부감이 없음</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>배치별 맛 차이 — 이전에 먹던 제품과 비교해 맛이 달라진 느낌을 받음</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2950,53 +3466,53 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +저당단백칩+고단백질바 증정</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>23,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261012194439_ca432aa40ade470f97d3ad13c56af534.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>908</v>
+        <v>21</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>달콤한 옥수수 스프맛 — 초당 옥수수 콘스프 맛으로 비리지 않고 달콤하게 먹기 좋음</t>
+          <t>확실한 숙취 해소 — 음주 전후 섭취 시 다음 날 숙취와 몸의 무거움이 확연히 덜함</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>속 더부룩함 개선 — 식후 섭취 시 소화가 원활하고 속이 편안해짐</t>
+          <t>간편한 스틱 형태 — 21ml 소용량 스틱형으로 휴대가 편하고 물 없이 바로 섭취 가능함</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>알찬 사은품 구성 — 10포 추가 증정 및 단백칩, 단백질바 증정 구성이 만족스러움</t>
+          <t>선물세트 패키지 — 보라색 박스와 쇼핑백 구성이 고급스러워 선물용으로 제격임</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>기존 대비 맛 차이 — 기존에 먹던 제품 버전과 맛 차이가 다소 느껴짐</t>
+          <t>진한 한약재 맛 — 쌍화탕이나 한약 느낌의 쓴맛이 돌아 호불호가 갈릴 수 있음</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -3040,23 +3556,19 @@
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>1915</v>
+        <v>1918</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>운동 수행 능력 향상 — 섭취 2~3주 후 운동 세트 횟수가 유지 및 증가하며 덜 지침</t>
+          <t>운동 수행능력 향상 — 섭취 2~3주 후 세트 후반 반복 횟수 및 운동 볼륨 유지에 도움 체감함</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>부드러운 풀림 — 입자가 뭉침 없이 잘 녹아 보충제나 음료에 섞어 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>센스 있는 헬스 선물 — 운동하는 지인이나 헬스 입문자에게 선물용으로 인기가 높음</t>
-        </is>
-      </c>
+          <t>우수한 풀림성 — 물에 잘 섞여 섭취하기 편리함</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -3064,7 +3576,7 @@
     <row r="19" ht="38" customHeight="1">
       <c r="B19" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3072,58 +3584,66 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
+          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백+소시지꼬치 오리지널맛 1개</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>삼대오백</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>45,900원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10908258</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261007162359_e049ea90261c452fae5a5a6f6ff7e802.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>1183</v>
+        <v>155</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>맛있는 매실맛 — 향이 좋고 맛있는 매실 맛으로 거부감 없이 음용 가능함</t>
+          <t>뛰어난 포만감 — 한 개만 먹어도 든든하여 식단 관리 및 다이어트에 도움 됨</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>우수한 풀림성 — 찬물에도 가루가 잘 풀려 운동 중 수분 보충용으로 마시기 편함</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>운동 전해질 보충 — 섭취 시 운동 수행 능력 향상 및 체력 유지에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+          <t>다양한 맛 구성 — 떡볶이 등 소스 맛이 뛰어나 닭가슴살을 질리지 않게 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>배송 오발송 및 누락 — 주문한 옵션과 다르게 구성품이 누락되거나 중복 배송됨</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>포장 불량 및 터짐 — 비닐 진공 포장이 헐렁해 일부 팩이 터져 소스가 묻어 배송됨</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>다소 자극적인 간 — 소스의 간이 생각보다 세서 단독 섭취 시 짤 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3131,55 +3651,51 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>삼대오백</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/10908258</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261007162359_e049ea90261c452fae5a5a6f6ff7e802.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>1535</v>
+        <v>1185</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>알찬 활력 조합 — 아르기닌과 밀크씨슬(마카) 조합으로 일상 및 운동 활력 충전에 효과적임</t>
+          <t>맛있는 음용감 — 매실맛, 알로에맛 등 음료처럼 마시기 좋고 향이 우수함</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>기상 시 개운함 — 꾸준히 섭취 시 아침에 일어날 때 몸이 한결 가볍고 피로가 줄어듦</t>
+          <t>찬물 풀림성 우수 — 가루가 뭉치지 않고 물에 잘 풀려 운동 중 수분 보충으로 적합함</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>선물용 쇼핑백 제공 — 패키지와 쇼핑백 동봉으로 직장인 및 지인 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>쇼핑백 불량 배송 — 증정용 쇼핑백의 손잡이 끈이 누락되어 배송됨</t>
-        </is>
-      </c>
+          <t>운동 활력 체감 — 섭취 유무에 따른 운동 시 컨디션 및 에너지 차이를 느낌</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
@@ -3194,12 +3710,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"닭가슴살 완벽세트" 보냉백+한끼통살 닭가슴살 15팩 세트</t>
+          <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3209,38 +3725,34 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10892246</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260518144708_605bd6c19e8d44cf8257b6dd6cb12c59.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>15</v>
+        <v>1535</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>다양한 맛과 촉촉함 — 소시지, 그릴드 등 종류가 다채롭고 질리지 않으며 맛이 좋음</t>
+          <t>피로 완화 및 활력 — 아침 기상 시 몸이 가볍고 운동 시 집중도와 지구력이 향상됨</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>실용적인 보냉백 증정 — 도시락용으로 들고 다니기 좋은 넉넉한 크기의 보냉백을 증정함</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>뛰어난 가성비 — 15팩 세트에 보냉백까지 포함되어 가격 대비 구성이 알참</t>
-        </is>
-      </c>
+          <t>실속 있는 영양 조합 — 아르기닌과 밀크씨슬을 한 번에 2개월분으로 챙길 수 있어 알참</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>이물질(뼈) 발견 — 섭취 중 단단한 닭 뼈 조각이 씹히는 현상이 발생함</t>
+          <t>사은품 불량 — 동봉된 쇼핑백의 끈이 누락된 상태로 배송됨</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -3402,7 +3914,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3971,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>고려은단</t>
         </is>
       </c>
     </row>
@@ -3516,7 +4028,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>올인원 명품비타민 이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 선물</t>
+          <t>고함량 비타민C 고려은단 메가도스C 3000 100포 / 분말비타민C</t>
         </is>
       </c>
     </row>
@@ -3564,10 +4076,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16258</v>
+        <v>16259</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15594</v>
+        <v>15597</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3402</v>
@@ -3576,7 +4088,7 @@
         <v>6514</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>8748</v>
@@ -3591,7 +4103,7 @@
         <v>1762</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>29858</v>
+        <v>956</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -3602,69 +4114,68 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 체감 — 피곤한 날 섭취 시 활력이 돋고 덜 피곤해지는 느낌을 받음
-선물용 만족도 — 인지도가 높고 고급스러운 이미지라 선물용 및 수령용으로 만족도가 높음</t>
+          <t>피로 해소 체감 — 섭취 후 덜 피곤하고 활력이 생기는 체감 효과 있음
+선물용으로 적합 — 인지도가 높고 센스 있는 선물로 만족도가 큼</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>활력 및 피로 개선 — 피로 누적 시 섭취하면 기운이 나고 자양강장 효과를 체감함
-선물 만족도 — 환절기나 시험 응원 등 지인 건강 선물용으로 적합함</t>
+          <t>편리한 복용 방식 — 물 없이 정제와 액상을 함께 먹을 수 있어 섭취 및 휴대 용이함
+피로 회복 체감 — 누적된 피로가 덜하고 활력 충전되는 느낌을 받음
+고급스러운 포장 — 남색과 오렌지 포인트 패키지가 깔끔하고 선물용으로 고급스러움</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>확실한 피로 개선 — 복용 후 다음 날 피로감이 덜하고 몸에 활력이 생기는 것을 체감함
-진한 액상 제형 — 다른 액상 비타민 대비 맛이 진하고 섭취하기 좋음
-선물 및 포장 만족 — 포장이 꼼꼼하여 받는 사람과 주는 사람 모두 만족도가 높음</t>
+          <t>활력 및 피로 개선 — 섭취 다음 날 몸의 활력이 생기고 덜 피곤한 느낌을 받음
+진한 액상 제형 — 타사 액상 제품 대비 농도가 진하여 만족스러움
+선물용 만족도 — 포장이 꼼꼼하고 선물용으로 주고받기 적합함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 새콤달콤하고 쫀득한 젤리 맛으로 간식처럼 거부감 없이 섭취 가능함
-간편한 복용법 — 알약을 잘 삼키지 못하는 사람도 물 없이 쉽게 먹을 수 있음
-귀여운 패키지 — 감귤 손잡이 모양 패키지와 귀여운 사은품으로 선물용으로 좋음</t>
+          <t>맛있는 젤리 제형 — 새콤달콤한 맛과 쫀득한 식감으로 간식처럼 거부감 없이 섭취 가능함
+쉬운 복용 편의성 — 알약을 삼키기 어려워하는 사람도 부담 없이 영양을 챙길 수 있음
+귀여운 선물 구성 — 선물 포장과 패키지가 귀엽고 키캡 등 증정품 만족도가 높음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 — 복용 후 오후 시간대 눈의 피로나 체력 저하가 줄어들고 에너지가 충전됨
-간편한 휴대 섭취 — 개별 포장으로 출근길이나 야외에서 물 없이 바로 섭취 가능함</t>
+          <t>빠른 피로 회복 체감 — 복용 후 며칠 지나지 않아 눈의 피로나 체력 저하 완화에 도움을 줌
+간편한 휴대 및 섭취 — 물 없이 간편하게 먹을 수 있고 개별 포장으로 휴대가 용이함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>컨디션 회복 효과 — 섭취 후 다음 날 아침 일어날 때 피로감이 덜하고 개운함
-편리한 휴대성 — 알약과 액상이 세트로 개별 포장되어 외출 시 가방에 넣고 다니기 편함
-고급스러운 포장 — 패키지가 깔끔하고 고급스러워 선물용으로 실용적임</t>
+          <t>간편한 개별 포장 — 외출 시 가방에 챙겨 다니며 간편하게 섭취 가능함
+다음 날 컨디션 회복 — 자기 전이나 피로 시 섭취하면 다음 날 아침 컨디션 개선을 체감함
+부담 없는 맛 — 맛이 자극적이거나 거부감 없이 무난함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>간편한 일일 섭취 — 1병씩 개별 포장되어 출근길이나 일상에서 간편하게 챙겨 먹기 좋음
-고급스러운 포장 — 패키지 포장이 예뻐 명절이나 기념일 선물용으로 적합함
-환절기 활력 충전 — 체력이 떨어지는 환절기 컨디션 및 면역 관리에 도움을 줌</t>
+          <t>선물용 패키지 만족 — 포장이 깔끔하고 예뻐 명절이나 기념일 선물로 좋음
+환절기 활력 충전 — 출근 시 챙겨 먹기 좋고 환절기 컨디션 및 활력 관리에 유용함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤 구성 — 남성과 여성용 비타민이 구분되어 있어 맞춤 선택이 가능함
-부담 없는 맛 — 비타민 특유의 쓴맛이 없고 진득하여 복용하기 수월함
-피로 개선 효과 — 직장인 필수 아이템으로 불릴 만큼 섭취 후 활력과 힘이 남</t>
+          <t>성별 맞춤 옵션 — 남성과 여성을 위한 비타민이 각각 구분되어 있어 유용함
+부담 없는 섭취감 — 특유의 쓴맛이 없고 휴대하며 간편하게 복용하기 좋음
+직장인 활력 충전 — 피로할 때 섭취하면 활력 증진에 도움 됨</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>신선한 혼합 방식 — 버튼을 눌러 분말과 액상을 즉석에서 섞어 먹는 방식이 신선하고 재미있음
-빠른 피로 회복 — 섭취 직후 즉각적으로 기운이 나고 피로 회복 체감이 뛰어남
-선물용 패키지 — 각 잡힌 박스 포장과 깔끔한 구성으로 선물하기 좋음</t>
+          <t>신선한 혼합 방식 — 캡을 누르면 분말이 액상과 섞이는 독특한 형태로 신선하게 섭취 가능함
+빠른 활력 회복 — 복용 후 피로 개선과 에너지 충전 효과를 빠르게 느낌
+호불호 없는 맛 — 맛에 거부감이 없고 액상형이라 목넘김이 편함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>간편한 올인원 섭취 — 물 없이 하루 한 병으로 간편하게 비타민을 보충할 수 있음
-피로 해소 체감 — 복용 후 아침 기상 시 개운함이 다르고 활력이 충전됨
-선물 포장 및 젤리 증정 — 쇼핑백과 박스 포장이 튼튼하며 추가 젤리 증정 구성에 대한 만족도가 높음</t>
+          <t>피로 완화 체감 — 복용 후 덜 피곤하고 피부 및 컨디션 관리에 도움 됨
+믿을 수 있는 원료 — 영국산 비타민C 원료를 사용하여 브랜드 신뢰도가 높음</t>
         </is>
       </c>
     </row>
@@ -3676,30 +4187,38 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>소비기한 아쉬움 — 잔여 소비기한이 기대보다 짧은 제품이 배송되어 아쉬움</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>배송 지연 — 배송이 너무 늦게 도착하여 불만족스러움</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
+          <t>아쉬운 소비기한 — 소비기한이 11개월가량 지난 재고 상품을 수령하여 실망스러움</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>다소 아쉬운 맛 — 액상 비타민 특성상 맛 자체는 아쉬움이 있음</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>배송 포장 아쉬움 — 쇼핑백 미동봉 및 일반 박스 포장으로 배송되어 선물용으로 아쉬움</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr"/>
+          <t>배송 포장 아쉬움 — 쇼핑백 없이 본품 박스만 단독 배송되어 포장 상태가 다소 당황스러움</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>다소 적은 부피감 — 소포장이라 선물용 외형이 풍성해 보이지 않음</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>섭취 후 목메임 — 혼합액 음용 후 목이 메여 물을 따로 마셔야 하는 번거로움이 있음</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+          <t>음용 시 목 메임 — 혼합액 음용 후 목이 메여 물을 따로 챙겨 마셔야 함</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>강한 신맛 — 분말 특성상 맛이 매우 셔서 먹기 부담스러울 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -3754,7 +4273,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>21,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
     </row>
@@ -3907,37 +4426,37 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
           <t>피부/미용</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -3964,42 +4483,42 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
           <t>아일로</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>삼대오백</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>삼대오백</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>삼대오백</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>익스트림</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
         </is>
       </c>
     </row>
@@ -4011,34 +4530,34 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로저당씬칩+빅맥세트(기프티콘)증정</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
           <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로저당씬칩+빅맥세트(기프티콘)증정</t>
-        </is>
-      </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
           <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
-        </is>
-      </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +저당단백칩+파로저당견과류바 증정</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
           <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +저당단백칩+고단백질바 증정</t>
-        </is>
-      </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
           <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
@@ -4046,17 +4565,17 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백+소시지꼬치 오리지널맛 1개</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
           <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>"닭가슴살 완벽세트" 보냉백+한끼통살 닭가슴살 15팩 세트</t>
         </is>
       </c>
     </row>
@@ -4104,34 +4623,34 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
+        <v>1697</v>
+      </c>
+      <c r="D19" s="3" t="n">
         <v>244</v>
       </c>
-      <c r="D19" s="3" t="n">
-        <v>1697</v>
-      </c>
       <c r="E19" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>755</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>68</v>
-      </c>
       <c r="G19" s="3" t="n">
+        <v>908</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>908</v>
-      </c>
       <c r="I19" s="3" t="n">
-        <v>1915</v>
+        <v>1918</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1183</v>
+        <v>155</v>
       </c>
       <c r="K19" s="3" t="n">
+        <v>1185</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>1535</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4142,74 +4661,69 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>달콤하고 맛있는 맛 — 맛이 거부감 없이 달달하여 부담 없이 섭취 가능함
-콜라보 디자인 — 리센느 에디션 패키지가 예쁘고 귀여워 소장 및 선물용으로 만족스러움</t>
+          <t>소화 편의성 체감 — 섭취 후 더부룩함이 덜하고 속이 편안해지는 느낌을 받음
+알찬 사은품 혜택 — 프로모션을 통한 단백질칩, 스낵, 기프티콘 등 다양한 증정 구성 만족스러움</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 소화감 — 섭취 후 속 더부룩함이 덜하고 편안해지는 느낌을 받음
-풍성한 증정품 혜택 — 톡딜 할인 가격에 단백질바, 씬칩, 기프티콘 등 다양한 사은품을 함께 제공함
-고급스러운 포장 — 선물 포장이 고급스러워 본인 사용 및 지인 선물용으로 모두 만족함</t>
+          <t>맛있는 단맛 — 달달하고 맛있어서 부담 없이 챙겨 먹기 좋음
+간편한 섭취 방식 — 물과 함께 가볍게 먹기 편함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 에디션 포장 — 오간자 패키지와 플리츠백 구성이 고급스러워 선물 개봉 시 만족감이 높음
-맛과 간편함 — 콜라겐 특유의 비린 맛 없이 맛있고 병 타입이라 섭취가 간편함</t>
+          <t>부드럽고 촉촉한 식감 — 닭가슴살 특유의 퍽퍽함 없이 촉촉하고 부드러움
+다양하고 맛있는 양념 — 떡볶이맛 등 소스가 다양하고 맛있어 질리지 않음
+간편한 조리 — 전자레인지로 데우기만 하면 되어 식단 관리에 편리함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>촉촉하고 맛있는 육질 — 퍽퍽하지 않고 촉촉하며 떡볶이맛 등 다양한 소스가 맛있음
-간편한 조리법 — 전자레인지에 간단히 데워 식단 관리나 간식으로 먹기 편리함
-높은 가성비 — 할인 행사를 통해 저렴한 가격에 쟁여두기 좋음</t>
+          <t>고급스러운 선물 포장 — 오간자 패키지와 플리츠백 구성이 매우 예쁘고 고급스러움
+맛있는 앰플 제형 — 비린 맛 없이 달콤하고 맛있어 매일 섭취하기 좋음</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>우수한 숙취 해소 — 음주 전후 섭취 시 다음 날 숙취와 몸의 무거움이 확연히 덜함
-간편한 스틱 휴대 — 작은 스틱 포 형태로 가방이나 주머니에 넣어 물 없이 바로 섭취 가능함
-고급스러운 선물 패키지 — 보라색 쇼핑백과 리본 손잡이 포장으로 술자리 지인 선물용으로 제격임</t>
+          <t>소화 및 배변 도움 — 식후 속 더부룩함이 줄어들고 배변 활동 및 몸이 가벼워지는 느낌을 받음
+맛있는 옥수수맛 — 콘스프처럼 달달하고 고소한 맛이라 거부감이 없음</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>달콤한 옥수수 스프맛 — 초당 옥수수 콘스프 맛으로 비리지 않고 달콤하게 먹기 좋음
-속 더부룩함 개선 — 식후 섭취 시 소화가 원활하고 속이 편안해짐
-알찬 사은품 구성 — 10포 추가 증정 및 단백칩, 단백질바 증정 구성이 만족스러움</t>
+          <t>확실한 숙취 해소 — 음주 전후 섭취 시 다음 날 숙취와 몸의 무거움이 확연히 덜함
+간편한 스틱 형태 — 21ml 소용량 스틱형으로 휴대가 편하고 물 없이 바로 섭취 가능함
+선물세트 패키지 — 보라색 박스와 쇼핑백 구성이 고급스러워 선물용으로 제격임</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>운동 수행 능력 향상 — 섭취 2~3주 후 운동 세트 횟수가 유지 및 증가하며 덜 지침
-부드러운 풀림 — 입자가 뭉침 없이 잘 녹아 보충제나 음료에 섞어 먹기 편함
-센스 있는 헬스 선물 — 운동하는 지인이나 헬스 입문자에게 선물용으로 인기가 높음</t>
+          <t>운동 수행능력 향상 — 섭취 2~3주 후 세트 후반 반복 횟수 및 운동 볼륨 유지에 도움 체감함
+우수한 풀림성 — 물에 잘 섞여 섭취하기 편리함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>맛있는 매실맛 — 향이 좋고 맛있는 매실 맛으로 거부감 없이 음용 가능함
-우수한 풀림성 — 찬물에도 가루가 잘 풀려 운동 중 수분 보충용으로 마시기 편함
-운동 전해질 보충 — 섭취 시 운동 수행 능력 향상 및 체력 유지에 도움을 줌</t>
+          <t>뛰어난 포만감 — 한 개만 먹어도 든든하여 식단 관리 및 다이어트에 도움 됨
+다양한 맛 구성 — 떡볶이 등 소스 맛이 뛰어나 닭가슴살을 질리지 않게 섭취 가능함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>알찬 활력 조합 — 아르기닌과 밀크씨슬(마카) 조합으로 일상 및 운동 활력 충전에 효과적임
-기상 시 개운함 — 꾸준히 섭취 시 아침에 일어날 때 몸이 한결 가볍고 피로가 줄어듦
-선물용 쇼핑백 제공 — 패키지와 쇼핑백 동봉으로 직장인 및 지인 선물용으로 적합함</t>
+          <t>맛있는 음용감 — 매실맛, 알로에맛 등 음료처럼 마시기 좋고 향이 우수함
+찬물 풀림성 우수 — 가루가 뭉치지 않고 물에 잘 풀려 운동 중 수분 보충으로 적합함
+운동 활력 체감 — 섭취 유무에 따른 운동 시 컨디션 및 에너지 차이를 느낌</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>다양한 맛과 촉촉함 — 소시지, 그릴드 등 종류가 다채롭고 질리지 않으며 맛이 좋음
-실용적인 보냉백 증정 — 도시락용으로 들고 다니기 좋은 넉넉한 크기의 보냉백을 증정함
-뛰어난 가성비 — 15팩 세트에 보냉백까지 포함되어 가격 대비 구성이 알참</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+          <t>피로 완화 및 활력 — 아침 기상 시 몸이 가볍고 운동 시 집중도와 지구력이 향상됨
+실속 있는 영양 조합 — 아르기닌과 밀크씨슬을 한 번에 2개월분으로 챙길 수 있어 알참</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="90" customHeight="1">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4217,33 +4731,43 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>적은 용량감 — 1포당 양이 다소 적게 느껴져 아쉬움
-쇼핑백 크기 부적합 — 동봉된 종이가방에 제품을 넣을 때 크기가 타이트하여 잘 들어가지 않음</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>다소 높은 가격대 — 정가 기준 가격대가 비싸 할인 시기에만 구매하게 됨</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
+          <t>가격 할인 아쉬움 — 평소 상시 판매 가격대에 대한 아쉬움이 있어 세일 요구가 있음</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>적은 용량 아쉬움 — 맛은 좋으나 1포당 용량이 다소 작게 느껴짐
+쇼핑백 크기 부적합 — 동봉된 종이가방에 제품을 넣을 때 규격이 빡빡하여 잘 안 들어감</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>비싼 정가 부담 — 평소 가격대가 다소 높아 할인 기간에만 구매하게 됨</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>배치별 맛 차이 — 이전에 먹던 제품과 비교해 맛이 달라진 느낌을 받음</t>
+        </is>
+      </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>기존 대비 맛 차이 — 기존에 먹던 제품 버전과 맛 차이가 다소 느껴짐</t>
+          <t>진한 한약재 맛 — 쌍화탕이나 한약 느낌의 쓴맛이 돌아 호불호가 갈릴 수 있음</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>쇼핑백 불량 배송 — 증정용 쇼핑백의 손잡이 끈이 누락되어 배송됨</t>
-        </is>
-      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>배송 오발송 및 누락 — 주문한 옵션과 다르게 구성품이 누락되거나 중복 배송됨
+포장 불량 및 터짐 — 비닐 진공 포장이 헐렁해 일부 팩이 터져 소스가 묻어 배송됨
+다소 자극적인 간 — 소스의 간이 생각보다 세서 단독 섭취 시 짤 수 있음</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>이물질(뼈) 발견 — 섭취 중 단단한 닭 뼈 조각이 씹히는 현상이 발생함</t>
+          <t>사은품 불량 — 동봉된 쇼핑백의 끈이 누락된 상태로 배송됨</t>
         </is>
       </c>
     </row>
@@ -4255,34 +4779,34 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
+          <t>41,900원</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
           <t>26,900원</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>41,900원</t>
-        </is>
-      </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
+          <t>33,000원</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
           <t>65,900원</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>33,000원</t>
-        </is>
-      </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t>23,900원</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
           <t>33,200원</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>23,900원</t>
-        </is>
-      </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
           <t>17,900원</t>
@@ -4290,12 +4814,12 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>45,900원</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
           <t>27,900원</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>25,900원</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -4490,7 +5014,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4498,7 +5022,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 침향환 9환 9일분</t>
+          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4508,48 +5032,44 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157094&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157053&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260826/o7EiJdX7BYMCuTvEmVmE919157094_00_01o7EiJdX7BYMCuTvEmVmE.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260327/PrU3TzDbYVJKWXoKyRxC919157053_00_01PrU3TzDbYVJKWXoKyRxC.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>201</v>
+        <v>750</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>압도적인 가성비 — 5,000원에 침향환 9환을 구매할 수 있어 가격 대비 구성이 훌륭함</t>
+          <t>압도적인 가성비 — 저렴한 가격으로 부담 없이 6년근 홍삼을 챙길 수 있음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>깔끔하고 정성스런 포장 — 패키지가 정성스럽고 깔끔하여 부모님 건강 간식용으로 좋음</t>
+          <t>무난하고 순한 맛 — 고가 제품과 유사한 맛이 나며 자극적이지 않고 먹기 편함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>취향 타는 맛 — 한방 환 특유의 맛으로 인해 젊은 층에서는 호불호가 갈림</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4557,7 +5077,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4572,28 +5092,28 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>2887</v>
+        <v>7265</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>위에 부담 없는 섭취 — 위가 약한 사람도 속 쓰림 부담 없이 매일 먹기 편안함</t>
+          <t>높은 가성비 — 대웅제약 브랜드 신뢰도 대비 가격이 매우 저렴함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>합리적인 데일리 비타민 — 대웅제약 브랜드 제품을 부담 없는 가격에 데일리로 섭취하기 좋음</t>
+          <t>부담 없는 섭취 — 한 달 분량으로 매일 꾸준히 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -4612,50 +5132,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>동화 부채표 배도라지쌍화 5포 5일분</t>
+          <t>대웅제약 밀크씨슬 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618637&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000134&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/xHnNEgPvPnLilc6RIN7P601618637_00_00xHnNEgPvPnLilc6RIN7P.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/bzKNvkJzwy2KdAqrXtDQ600000134_00_00bzKNvkJzwy2KdAqrXtDQ.png</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>466</v>
+        <v>4061</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>목 칼칼함 및 기침 완화 — 환절기 목이 칼칼하거나 기침이 날 때 마시면 몸이 따뜻해짐</t>
+          <t>뛰어난 가성비 — 저렴한 가격 대비 품질이 만족스러워 재구매율이 높음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>달달하고 진한 풍미 — 배, 도라지, 쌍화의 맛이 쓰지 않고 달콤하게 어우러져 마시기 편함</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>요리 활용성 — 건강 음료 섭취 외에 족발이나 삼계탕 조리용으로도 활용됨</t>
-        </is>
-      </c>
+          <t>간편한 간 건강 관리 — 부모님 선물이나 일상적인 피로 관리에 챙기기 용이함</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -4671,54 +5187,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 MSM 90정 30일분</t>
+          <t>[강력한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 스트롱민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000149&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911101&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/gVoECGdnaBQU8HtRPGFz600000149_00_00gVoECGdnaBQU8HtRPGFz.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/BQeSyYNH21gmMrEclYYV610911101_00_01BQeSyYNH21gmMrEclYYV.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>1042</v>
+        <v>231</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>저렴한 관절 영양제 — 약사 추천 성분인 MSM을 매우 저렴한 가격에 구매 가능함</t>
+          <t>강렬한 구강 상쾌함 — 터뜨리는 순간 목과 입안이 화해지며 텁텁함과 구취가 빠르게 해소됨</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>복합 섭취 용이성 — 콘드로이친 등 다른 관절 제품과 함께 부담 없이 챙겨 먹기 좋음</t>
+          <t>프로폴리스 성분 함유 — 목 관리와 청량감을 동시에 챙길 수 있어 휴대용으로 좋음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>사용감 불만족 — 가글 대비 효과가 떨어지거나 기호에 맞지 않는다는 의견 있음</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4726,12 +5246,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>홀베리 유기농 레몬자몽즙 10포</t>
+          <t>안국약품 브이팩 다이어트 유산균 올인원 멀티 비타민 7포</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4741,32 +5261,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923433&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=968235549&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260904/CHKuI8IOm2jKkPhjWAjw965923433_00_00CHKuI8IOm2jKkPhjWAjw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/kQh0cYBVEEUhZLYsuKrQ968235549_00_00kQh0cYBVEEUhZLYsuKrQ.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>727</v>
+        <v>712</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>상큼한 맛과 가성비 — 운동할 때 물에 타서 가볍게 레몬자몽수로 마시기 좋음</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>편리한 개별 포장 — 하루 한 팩에 필요한 정제가 들어 있어 휴대 및 외출 시 섭취가 간편함</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>올인원 관리 — 여러 영양제 통을 챙길 필요 없이 한 번에 관리 가능함</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>강한 신맛과 텁텁함 — 자몽 향이 약하고 레몬 맛이 너무 시거나 텁텁하여 물을 많이 타야 함</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -4781,12 +5301,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 샷 25ml x 5병 5일분</t>
+          <t>자연관 리프레쉬 마그네슘＆L-테아닌 4병 4일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4796,39 +5316,43 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000204&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627142&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251121/aHjoRwP9ejVVuu8M0Td4600000204_00_01aHjoRwP9ejVVuu8M0Td4.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260612/IiBr1SI0rlUycwbkaeGq032627142_00_01IiBr1SI0rlUycwbkaeGq.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1478</v>
+        <v>323</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>먹기 편한 액상 앰플 — 알약을 삼키기 힘든 사람도 적은 용량으로 빠르게 마실 수 있음</t>
+          <t>편리한 듀얼 성분 — 마그네슘과 L-테아닌이 함께 들어 있어 따로 챙길 필요가 없음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>피로 회복 및 야외 휴대 — 소용량 샷 형태로 등산이나 시험 기간 등 피로할 때 간편하게 챙기기 좋음</t>
+          <t>착한 가격 부담 없음 — 소용량으로 가격 부담 없이 필요할 때마다 구매해 섭취 가능함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>효과 체감 미미 — 스트레스 완화 효과에 대해 뚜렷한 체감을 느끼지 못함</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4836,58 +5360,54 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 구증구포 흑삼제로 5포 5일분</t>
+          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157054&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953535&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260327/zJhcupvR4JWL5xMXOnRP919157054_00_01zJhcupvR4JWL5xMXOnRP.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/nv6m1SoKa2Zw57OA3JHL994953535_00_00nv6m1SoKa2Zw57OA3JHL.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>401</v>
+        <v>1104</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>착한 가격대 — 저렴한 가격에 흑삼 성분을 간편하게 섭취할 수 있어 가성비가 우수함</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>부담 없는 달콤한 맛 — 거북하지 않고 달달한 꿀물 맛이라 편하게 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>저렴한 가격 — 식전 다이어트 보조용으로 저렴하게 구매해 시도하기 좋음</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>연한 농도와 맛 — 가격 대비 물맛이 많이 나고 맛이 다소 연함</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>재고 품귀 현상 — 매장이나 몰에서 구하기가 어려움</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4895,12 +5415,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
+          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4910,28 +5430,28 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157095&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602130&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260826/gxSEg0bfLulOAScPenvi919157095_00_01gxSEg0bfLulOAScPenvi.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250922/dxtu28UFPhWKbi5IG3n8613602130_00_01dxtu28UFPhWKbi5IG3n8.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>120</v>
+        <v>1662</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>높은 가성비 — 5,000원에 6년근 고려 홍삼환 9환을 구매할 수 있어 경제적임</t>
+          <t>맛있는 젤리 형태 — 간식처럼 쫄깃쫄깃하고 맛있어서 아이들이 먼저 찾아 먹음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>진한 맛과 개운함 — 맛이 깊고 진하며 저녁에 섭취 시 몸이 따뜻해지고 아침 기상이 개운함</t>
+          <t>간편한 복합 영양 섭취 — 비타민D와 아연을 하루 한 구미로 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -4950,7 +5470,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4960,33 +5480,33 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>6703</v>
+        <v>4205</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>우수한 가성비 — 혈행 건강을 위한 데일리 오메가3를 저렴한 가격에 구매 가능함</t>
+          <t>합리적인 가격대 — 꾸준히 챙겨 먹기 부담 없는 가성비 좋은 눈 영양제임</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>믿을 수 있는 제약사 — 대웅제약 브랜드 제품이라 신뢰하고 매일 챙겨 먹기 좋음</t>
+          <t>편리한 복용 — 한 달 분량으로 정제 섭취가 간편함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -4997,7 +5517,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5005,12 +5525,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 숙취해소 노니샷 5포 5회분</t>
+          <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5020,36 +5540,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000151&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982831&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250507/h6NVof0E9taNldehzI8v600000151_00_00h6NVof0E9taNldehzI8v.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/lX1R9GhsEUzz72XUg7VZ611982831_00_00lX1R9GhsEUzz72XUg7VZ.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>678</v>
+        <v>1557</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>저렴한 숙취해소제 — 타사 대비 매우 저렴한 가격으로 부담 없이 구비해두기 좋음</t>
+          <t>작은 미니 캡슐 크기 — 알약 크기가 매우 작아 목넘김이 편하고 한 번에 삼키기 쉬움</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>음주 후 속 진정 — 아침 숙취 시 섭취하면 속이 가라앉는 체감을 줌</t>
+          <t>가성비 및 적절한 분량 — 한 달 분량으로 질리지 않고 저렴하게 이용 가능함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>애매한 쓴맛과 효과 — 꿀맛과 쓴맛이 섞여 있고 사람에 따라 숙취 해소 체감이 모호함</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5164,27 +5680,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -5194,12 +5710,12 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -5209,7 +5725,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
     </row>
@@ -5231,42 +5747,42 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>안국약품</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>자연관</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>이너뷰 바이 리튠</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>오브맘</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>홀베리</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>휴럼</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>휴럼</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>안국약품</t>
         </is>
       </c>
     </row>
@@ -5278,52 +5794,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 침향환 9환 9일분</t>
+          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>동화 부채표 배도라지쌍화 5포 5일분</t>
+          <t>대웅제약 밀크씨슬 30정 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 MSM 90정 30일분</t>
+          <t>[강력한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 스트롱민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>홀베리 유기농 레몬자몽즙 10포</t>
+          <t>안국약품 브이팩 다이어트 유산균 올인원 멀티 비타민 7포</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 샷 25ml x 5병 5일분</t>
+          <t>자연관 리프레쉬 마그네슘＆L-테아닌 4병 4일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 구증구포 흑삼제로 5포 5일분</t>
+          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
+          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 숙취해소 노니샷 5포 5회분</t>
+          <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
         </is>
       </c>
     </row>
@@ -5334,34 +5850,34 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="G6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>4.8</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>4.9</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>4.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -5371,37 +5887,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>201</v>
+        <v>750</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2887</v>
+        <v>7265</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>466</v>
+        <v>4061</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1042</v>
+        <v>231</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>727</v>
+        <v>712</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1478</v>
+        <v>323</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>401</v>
+        <v>1104</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>120</v>
+        <v>1662</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>6703</v>
+        <v>4205</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5409,97 +5925,89 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>압도적인 가성비 — 5,000원에 침향환 9환을 구매할 수 있어 가격 대비 구성이 훌륭함
-깔끔하고 정성스런 포장 — 패키지가 정성스럽고 깔끔하여 부모님 건강 간식용으로 좋음</t>
+          <t>압도적인 가성비 — 저렴한 가격으로 부담 없이 6년근 홍삼을 챙길 수 있음
+무난하고 순한 맛 — 고가 제품과 유사한 맛이 나며 자극적이지 않고 먹기 편함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>위에 부담 없는 섭취 — 위가 약한 사람도 속 쓰림 부담 없이 매일 먹기 편안함
-합리적인 데일리 비타민 — 대웅제약 브랜드 제품을 부담 없는 가격에 데일리로 섭취하기 좋음</t>
+          <t>높은 가성비 — 대웅제약 브랜드 신뢰도 대비 가격이 매우 저렴함
+부담 없는 섭취 — 한 달 분량으로 매일 꾸준히 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>목 칼칼함 및 기침 완화 — 환절기 목이 칼칼하거나 기침이 날 때 마시면 몸이 따뜻해짐
-달달하고 진한 풍미 — 배, 도라지, 쌍화의 맛이 쓰지 않고 달콤하게 어우러져 마시기 편함
-요리 활용성 — 건강 음료 섭취 외에 족발이나 삼계탕 조리용으로도 활용됨</t>
+          <t>뛰어난 가성비 — 저렴한 가격 대비 품질이 만족스러워 재구매율이 높음
+간편한 간 건강 관리 — 부모님 선물이나 일상적인 피로 관리에 챙기기 용이함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 관절 영양제 — 약사 추천 성분인 MSM을 매우 저렴한 가격에 구매 가능함
-복합 섭취 용이성 — 콘드로이친 등 다른 관절 제품과 함께 부담 없이 챙겨 먹기 좋음</t>
+          <t>강렬한 구강 상쾌함 — 터뜨리는 순간 목과 입안이 화해지며 텁텁함과 구취가 빠르게 해소됨
+프로폴리스 성분 함유 — 목 관리와 청량감을 동시에 챙길 수 있어 휴대용으로 좋음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>상큼한 맛과 가성비 — 운동할 때 물에 타서 가볍게 레몬자몽수로 마시기 좋음</t>
+          <t>편리한 개별 포장 — 하루 한 팩에 필요한 정제가 들어 있어 휴대 및 외출 시 섭취가 간편함
+올인원 관리 — 여러 영양제 통을 챙길 필요 없이 한 번에 관리 가능함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>먹기 편한 액상 앰플 — 알약을 삼키기 힘든 사람도 적은 용량으로 빠르게 마실 수 있음
-피로 회복 및 야외 휴대 — 소용량 샷 형태로 등산이나 시험 기간 등 피로할 때 간편하게 챙기기 좋음</t>
+          <t>편리한 듀얼 성분 — 마그네슘과 L-테아닌이 함께 들어 있어 따로 챙길 필요가 없음
+착한 가격 부담 없음 — 소용량으로 가격 부담 없이 필요할 때마다 구매해 섭취 가능함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>착한 가격대 — 저렴한 가격에 흑삼 성분을 간편하게 섭취할 수 있어 가성비가 우수함</t>
+          <t>부담 없는 달콤한 맛 — 거북하지 않고 달달한 꿀물 맛이라 편하게 섭취 가능함
+저렴한 가격 — 식전 다이어트 보조용으로 저렴하게 구매해 시도하기 좋음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>높은 가성비 — 5,000원에 6년근 고려 홍삼환 9환을 구매할 수 있어 경제적임
-진한 맛과 개운함 — 맛이 깊고 진하며 저녁에 섭취 시 몸이 따뜻해지고 아침 기상이 개운함</t>
+          <t>맛있는 젤리 형태 — 간식처럼 쫄깃쫄깃하고 맛있어서 아이들이 먼저 찾아 먹음
+간편한 복합 영양 섭취 — 비타민D와 아연을 하루 한 구미로 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>우수한 가성비 — 혈행 건강을 위한 데일리 오메가3를 저렴한 가격에 구매 가능함
-믿을 수 있는 제약사 — 대웅제약 브랜드 제품이라 신뢰하고 매일 챙겨 먹기 좋음</t>
+          <t>합리적인 가격대 — 꾸준히 챙겨 먹기 부담 없는 가성비 좋은 눈 영양제임
+편리한 복용 — 한 달 분량으로 정제 섭취가 간편함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 숙취해소제 — 타사 대비 매우 저렴한 가격으로 부담 없이 구비해두기 좋음
-음주 후 속 진정 — 아침 숙취 시 섭취하면 속이 가라앉는 체감을 줌</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>작은 미니 캡슐 크기 — 알약 크기가 매우 작아 목넘김이 편하고 한 번에 삼키기 쉬움
+가성비 및 적절한 분량 — 한 달 분량으로 질리지 않고 저렴하게 이용 가능함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>취향 타는 맛 — 한방 환 특유의 맛으로 인해 젊은 층에서는 호불호가 갈림</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>강한 신맛과 텁텁함 — 자몽 향이 약하고 레몬 맛이 너무 시거나 텁텁하여 물을 많이 타야 함</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>연한 농도와 맛 — 가격 대비 물맛이 많이 나고 맛이 다소 연함
-재고 품귀 현상 — 매장이나 몰에서 구하기가 어려움</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>사용감 불만족 — 가글 대비 효과가 떨어지거나 기호에 맞지 않는다는 의견 있음</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>효과 체감 미미 — 스트레스 완화 효과에 대해 뚜렷한 체감을 느끼지 못함</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>애매한 쓴맛과 효과 — 꿀맛과 쓴맛이 섞여 있고 사람에 따라 숙취 해소 체감이 모호함</t>
-        </is>
-      </c>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -5509,39 +6017,39 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>2,000원</t>
-        </is>
-      </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>2,000원</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
@@ -5549,7 +6057,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5642,7 +6150,1071 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>이미지</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>가격</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>상품URL</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>이미지URL</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>리뷰평점</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>리뷰건수</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>긍정1</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>긍정2</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>긍정3</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>부정1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>부정2</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>부정3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[올영 단독/TWS 띠부실 증정] 미에로화이바 데이톡 14포 (14일분)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>미에로화이바</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>15,900원</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000237883&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023788363ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[올영 단독/TWS 띠부실 증정] 미에로화이바 브이캔디 20정 기획</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>미에로화이바</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9,500원</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000268343&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026834306ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>35,800원</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549621ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>30,400원</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>25,900원</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225906&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022590605ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>탄탄 더블컷 다이어트 젤리 2종 택1 (자두맛/애플유자맛)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>탄탄</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8,900원</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000213057&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021305744ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6244</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>17396</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>얼굴 붓기 개선 체감 — 촬영 전이나 야식 및 음주 후 섭취 시 얼굴 라인 관리에 도움 됨</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>작은 미니환 제형 — 크기가 작은 미니환 형태로 제작되어 목넘김이 편함</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>씨제이웰케어</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5,900원</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>콜라보 사은품 매력 — 산리오 카드홀더 등 아기자기한 증정 굿즈가 만족스러움</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>25848</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>초소형 캡슐 목넘김 — 캡슐 크기가 170mg으로 매우 작고 가벼워 삼키기 쉬움</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>질과 장 복합 케어 — 질 건강과 장 건강을 한 번에 꾸준히 관리할 수 있어 만족스러움</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>귀여운 에디션 굿즈 — 포켓몬 콜라보 카드케이스 증정 구성으로 구매 만족도를 높임</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>1위</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2위</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>3위</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>4위</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>5위</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>6위</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>7위</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>8위</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>9위</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>10위</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="100" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>썸네일</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>미에로화이바</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>미에로화이바</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>탄탄</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>씨제이웰케어</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>[올영 단독/TWS 띠부실 증정] 미에로화이바 데이톡 14포 (14일분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[올영 단독/TWS 띠부실 증정] 미에로화이바 브이캔디 20정 기획</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>탄탄 더블컷 다이어트 젤리 2종 택1 (자두맛/애플유자맛)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>평점</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>리뷰수</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="n">
+        <v>6244</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>17396</v>
+      </c>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="n">
+        <v>25848</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>긍정리뷰</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>얼굴 붓기 개선 체감 — 촬영 전이나 야식 및 음주 후 섭취 시 얼굴 라인 관리에 도움 됨
+작은 미니환 제형 — 크기가 작은 미니환 형태로 제작되어 목넘김이 편함</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>콜라보 사은품 매력 — 산리오 카드홀더 등 아기자기한 증정 굿즈가 만족스러움</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>초소형 캡슐 목넘김 — 캡슐 크기가 170mg으로 매우 작고 가벼워 삼키기 쉬움
+질과 장 복합 케어 — 질 건강과 장 건강을 한 번에 꾸준히 관리할 수 있어 만족스러움
+귀여운 에디션 굿즈 — 포켓몬 콜라보 카드케이스 증정 구성으로 구매 만족도를 높임</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>부정리뷰</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>판매가</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>15,900원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>9,500원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>35,800원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>30,400원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>25,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>8,900원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>5,900원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A11"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5671,6 +7243,11 @@
           <t>다이소몰</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5679,16 +7256,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>36.7</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -5701,12 +7281,15 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>26.7</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5717,111 +7300,195 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>16.7</v>
+        <v>17.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
